--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
@@ -1486,7 +1486,7 @@
       <c r="C30" s="111" t="n"/>
       <c r="D30" s="112" t="inlineStr">
         <is>
-          <t>직책 / 역할:</t>
+          <t>직책 / 역할: 품질책임자</t>
         </is>
       </c>
       <c r="E30" s="110" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
@@ -1495,7 +1495,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: [확인 필요]</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
@@ -1271,7 +1271,7 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>※ 복원 실패·내용 불일치 시 아래 행에 재점검 내용을 기록합니다(재점검 14~16행).</t>
+          <t>백업 실패 기록 (백업 실패 발생 시 작성)</t>
         </is>
       </c>
       <c r="B13" s="44" t="n"/>
@@ -1281,12 +1281,36 @@
       <c r="F13" s="44" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="44" t="n"/>
-      <c r="B14" s="44" t="n"/>
-      <c r="C14" s="44" t="n"/>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="44" t="n"/>
+      <c r="A14" s="45" t="inlineStr">
+        <is>
+          <t>실패 확인일</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>재실행 일자</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>재실행 결과(성공/불가)</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>불가 시 품질책임자 보고 일자(메일)</t>
+        </is>
+      </c>
+      <c r="E14" s="45" t="inlineStr">
+        <is>
+          <t>실패 원인·조치</t>
+        </is>
+      </c>
+      <c r="F14" s="45" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="44" t="n"/>
@@ -1383,7 +1407,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="95" t="inlineStr">
         <is>
-          <t>작성 안내: 매월 1회 서버 전체 파일 목록에서 스프레드시트 난수 함수로 3건을 무작위 선정하고, 백업에서 복원하여 열람·내용이 정상인지 확인합니다. 선정에 사용한 난수 값을 반드시 기록합니다. 복원 실패 시 조치 내용을 종합 판정란에 기록합니다.</t>
+          <t>작성 안내: 매월 1회 서버 전체 파일 목록에서 스프레드시트 난수 함수로 3건을 무작위 선정하고, 백업에서 복원하여 열람·내용이 정상인지 확인합니다. 선정에 사용한 난수 값을 반드시 기록합니다. 복원 실패 시 조치 내용을 종합 판정란에 기록합니다. 백업 실패 시 알림(메일)을 받은 날 실패 확인일을 기록하고, 다음날까지 재실행하며, 재실행이 불가능하면 확인한 당일 안에 품질책임자에게 메일로 보고하고 보고 일자를 기록합니다.</t>
         </is>
       </c>
       <c r="B23" s="96" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_백업복구점검기록_초안.xlsx
@@ -1,11 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="복구점검기록_초안" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="복구점검기록_초안" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'복구점검기록_초안'!$A$1:$F$32</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -1087,7 +1089,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1567,6 +1569,8 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>